--- a/data/trans_orig/P23-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P23-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el consumo de tabaco y/o marihuana/hachís, actual o pasado en 2007</t>
+          <t>Población según el consumo de tabaco y/o marihuana/hachís, actual o pasado en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>319053</t>
+          <t>319057</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>380439</t>
+          <t>379062</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1059108</t>
+          <t>1062291</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1112917</t>
+          <t>1114560</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1385589</t>
+          <t>1391396</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1481470</t>
+          <t>1481557</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>59,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>63,16%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>277289</t>
+          <t>279275</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>336848</t>
+          <t>339888</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>38881</t>
+          <t>37168</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>66963</t>
+          <t>66134</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>321102</t>
+          <t>326903</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>392560</t>
+          <t>391990</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,71%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10258</t>
+          <t>10353</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26370</t>
+          <t>27357</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4150</t>
+          <t>4257</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15478</t>
+          <t>16682</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>16563</t>
+          <t>18004</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>37627</t>
+          <t>39617</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>327151</t>
+          <t>327110</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>386937</t>
+          <t>386572</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>145501</t>
+          <t>143465</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>193542</t>
+          <t>191107</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>487986</t>
+          <t>484460</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>571250</t>
+          <t>567600</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,2%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>597655</t>
+          <t>600144</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>677701</t>
+          <t>682780</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>40,32%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>846373</t>
+          <t>846842</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>922285</t>
+          <t>924305</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>53,31%</t>
+          <t>53,34%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>58,22%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1461774</t>
+          <t>1470001</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1575411</t>
+          <t>1586542</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>48,35%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>208916</t>
+          <t>209920</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>268406</t>
+          <t>266912</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>131170</t>
+          <t>132240</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>178875</t>
+          <t>179581</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>357898</t>
+          <t>355563</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>429700</t>
+          <t>428692</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,07%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35107</t>
+          <t>35663</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>63591</t>
+          <t>62949</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>38151</t>
+          <t>38441</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>64586</t>
+          <t>65468</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>80187</t>
+          <t>81744</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>120317</t>
+          <t>120177</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>728246</t>
+          <t>725438</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>809084</t>
+          <t>809888</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>47,83%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>462213</t>
+          <t>463378</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>535998</t>
+          <t>536546</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1214291</t>
+          <t>1211017</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1324378</t>
+          <t>1321042</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>40,26%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>249329</t>
+          <t>248436</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>296602</t>
+          <t>296222</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>53,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>262246</t>
+          <t>266561</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>306104</t>
+          <t>309076</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,05%</t>
+          <t>55,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,25%</t>
+          <t>64,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>527562</t>
+          <t>528022</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>592071</t>
+          <t>593386</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>57,6%</t>
+          <t>57,73%</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>68001</t>
+          <t>68195</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>103995</t>
+          <t>102422</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>39705</t>
+          <t>38040</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>65431</t>
+          <t>65233</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>114513</t>
+          <t>114911</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>160403</t>
+          <t>159466</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,51%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11773</t>
+          <t>10830</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28198</t>
+          <t>28374</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17814</t>
+          <t>17285</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>37987</t>
+          <t>37158</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32971</t>
+          <t>32963</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>58025</t>
+          <t>60060</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,84%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>153608</t>
+          <t>153522</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>197293</t>
+          <t>198588</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>93988</t>
+          <t>94150</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>134347</t>
+          <t>130995</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>260508</t>
+          <t>255563</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>318969</t>
+          <t>315554</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>30,7%</t>
         </is>
       </c>
     </row>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1200076</t>
+          <t>1203141</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1310485</t>
+          <t>1316105</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2203911</t>
+          <t>2202130</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2311143</t>
+          <t>2308664</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>65,22%</t>
+          <t>65,17%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>68,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3434762</t>
+          <t>3439197</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3594076</t>
+          <t>3600392</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>51,68%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>54,1%</t>
         </is>
       </c>
     </row>
@@ -2552,12 +2552,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>588377</t>
+          <t>584210</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>674870</t>
+          <t>674534</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2587,12 +2587,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>228119</t>
+          <t>227951</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>290133</t>
+          <t>286169</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>831236</t>
+          <t>831198</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>939946</t>
+          <t>939920</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2665,12 +2665,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>68477</t>
+          <t>70808</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>103539</t>
+          <t>106217</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>68458</t>
+          <t>68275</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>103844</t>
+          <t>102893</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>147719</t>
+          <t>145101</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>196882</t>
+          <t>197464</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1243869</t>
+          <t>1246038</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1358298</t>
+          <t>1358779</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>41,48%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>734097</t>
+          <t>734624</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>832959</t>
+          <t>826978</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2004640</t>
+          <t>2001220</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2158558</t>
+          <t>2163486</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>32,51%</t>
         </is>
       </c>
     </row>
@@ -3044,7 +3044,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el consumo de tabaco y/o marihuana/hachís, actual o pasado en 2012</t>
+          <t>Población según el consumo de tabaco y/o marihuana/hachís, actual o pasado en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>222501</t>
+          <t>222009</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>280378</t>
+          <t>280882</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1035523</t>
+          <t>1037062</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1094065</t>
+          <t>1094126</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>77,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>81,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1266597</t>
+          <t>1270853</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1365547</t>
+          <t>1364848</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>54,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>59,02%</t>
         </is>
       </c>
     </row>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>355887</t>
+          <t>358530</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>423836</t>
+          <t>422426</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3367,12 +3367,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3387,12 +3387,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>55774</t>
+          <t>56718</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>87388</t>
+          <t>91721</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3422,12 +3422,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>419388</t>
+          <t>422254</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>498309</t>
+          <t>500473</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,64%</t>
         </is>
       </c>
     </row>
@@ -3465,12 +3465,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10236</t>
+          <t>10433</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30120</t>
+          <t>29103</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3480,12 +3480,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3500,12 +3500,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3262</t>
+          <t>4116</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14910</t>
+          <t>15270</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3535,12 +3535,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>16951</t>
+          <t>17028</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>38151</t>
+          <t>39430</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -3578,12 +3578,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>286126</t>
+          <t>290049</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>345932</t>
+          <t>346980</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3613,12 +3613,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>165616</t>
+          <t>165253</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>218419</t>
+          <t>215774</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3628,12 +3628,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3648,12 +3648,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>466174</t>
+          <t>470650</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>549540</t>
+          <t>549617</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3663,12 +3663,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,77%</t>
         </is>
       </c>
     </row>
@@ -3808,12 +3808,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>711283</t>
+          <t>711715</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>796209</t>
+          <t>797689</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>40,64%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3843,12 +3843,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>832923</t>
+          <t>831181</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>919616</t>
+          <t>919061</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>47,44%</t>
+          <t>47,34%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>52,34%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3878,12 +3878,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1559901</t>
+          <t>1561788</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1690040</t>
+          <t>1691670</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>42,0%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>45,49%</t>
         </is>
       </c>
     </row>
@@ -3921,12 +3921,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>317531</t>
+          <t>318078</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>388967</t>
+          <t>387303</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3936,12 +3936,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3956,12 +3956,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>216037</t>
+          <t>212901</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>274828</t>
+          <t>274002</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3971,12 +3971,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3991,12 +3991,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>553200</t>
+          <t>554733</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>645172</t>
+          <t>645095</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -4034,12 +4034,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>43397</t>
+          <t>44767</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>73852</t>
+          <t>74153</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4049,12 +4049,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>34786</t>
+          <t>35653</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>64219</t>
+          <t>64597</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>85587</t>
+          <t>86272</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>130013</t>
+          <t>127159</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4119,12 +4119,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -4147,12 +4147,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>754435</t>
+          <t>753386</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>843790</t>
+          <t>843391</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4162,12 +4162,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>42,97%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>548592</t>
+          <t>545517</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>627030</t>
+          <t>629208</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4197,12 +4197,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>35,84%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1321102</t>
+          <t>1331262</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1443675</t>
+          <t>1443917</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4232,12 +4232,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>38,83%</t>
         </is>
       </c>
     </row>
@@ -4377,12 +4377,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>199972</t>
+          <t>199605</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>248088</t>
+          <t>245418</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4392,12 +4392,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>41,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>217135</t>
+          <t>217064</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>261959</t>
+          <t>263390</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4427,12 +4427,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,12%</t>
+          <t>57,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>431523</t>
+          <t>432392</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>497562</t>
+          <t>499273</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4462,12 +4462,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>52,94%</t>
+          <t>53,12%</t>
         </is>
       </c>
     </row>
@@ -4490,12 +4490,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>80031</t>
+          <t>79506</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>115665</t>
+          <t>117488</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4505,12 +4505,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>63017</t>
+          <t>62577</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>97055</t>
+          <t>96674</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4540,12 +4540,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>151185</t>
+          <t>153467</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>203007</t>
+          <t>204606</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4575,12 +4575,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,77%</t>
         </is>
       </c>
     </row>
@@ -4603,12 +4603,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11246</t>
+          <t>11701</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31726</t>
+          <t>29904</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4618,12 +4618,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4638,12 +4638,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9592</t>
+          <t>10002</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27241</t>
+          <t>26689</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4653,12 +4653,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4673,12 +4673,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25609</t>
+          <t>26205</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>51995</t>
+          <t>52154</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4688,12 +4688,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -4716,12 +4716,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>123190</t>
+          <t>123805</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>164711</t>
+          <t>166070</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4731,12 +4731,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4751,12 +4751,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>103741</t>
+          <t>103377</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>144897</t>
+          <t>144601</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4766,12 +4766,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4786,12 +4786,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>235521</t>
+          <t>232267</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>293170</t>
+          <t>292236</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4801,12 +4801,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>31,1%</t>
         </is>
       </c>
     </row>
@@ -4946,12 +4946,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1169214</t>
+          <t>1166193</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1287079</t>
+          <t>1283401</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4961,12 +4961,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4981,12 +4981,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2118855</t>
+          <t>2121879</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2239256</t>
+          <t>2242001</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4996,12 +4996,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>59,73%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>63,04%</t>
+          <t>63,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5016,12 +5016,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3317980</t>
+          <t>3326348</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3494974</t>
+          <t>3494725</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>47,72%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>50,13%</t>
         </is>
       </c>
     </row>
@@ -5059,12 +5059,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>785654</t>
+          <t>786706</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>891878</t>
+          <t>893038</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5074,12 +5074,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5094,12 +5094,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>355394</t>
+          <t>356040</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>430365</t>
+          <t>432779</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5109,12 +5109,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1166686</t>
+          <t>1162151</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1298429</t>
+          <t>1298074</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5144,12 +5144,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,62%</t>
         </is>
       </c>
     </row>
@@ -5172,12 +5172,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>76325</t>
+          <t>75557</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>116124</t>
+          <t>116205</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -5207,12 +5207,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>58606</t>
+          <t>57773</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>94138</t>
+          <t>92297</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5222,12 +5222,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5242,12 +5242,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>142155</t>
+          <t>144431</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>196368</t>
+          <t>198152</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5257,12 +5257,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -5285,12 +5285,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1197587</t>
+          <t>1202577</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1314936</t>
+          <t>1315793</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5300,12 +5300,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>38,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5320,12 +5320,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>849511</t>
+          <t>851364</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>955509</t>
+          <t>960543</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5335,12 +5335,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2081569</t>
+          <t>2080552</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2250913</t>
+          <t>2241575</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5370,12 +5370,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>32,16%</t>
         </is>
       </c>
     </row>
@@ -5551,7 +5551,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el consumo de tabaco y/o marihuana/hachís, actual o pasado en 2016</t>
+          <t>Población según el consumo de tabaco y/o marihuana/hachís, actual o pasado en 2016 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5746,12 +5746,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>264354</t>
+          <t>262805</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>317445</t>
+          <t>316716</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5761,12 +5761,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>782595</t>
+          <t>780563</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>831147</t>
+          <t>833736</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5816,12 +5816,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1055668</t>
+          <t>1055490</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1135239</t>
+          <t>1136592</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5831,12 +5831,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>60,47%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,03%</t>
+          <t>65,11%</t>
         </is>
       </c>
     </row>
@@ -5859,12 +5859,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>215306</t>
+          <t>216545</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>265037</t>
+          <t>265668</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5874,12 +5874,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36699</t>
+          <t>35961</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>64840</t>
+          <t>64097</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5909,12 +5909,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>259198</t>
+          <t>260530</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>320587</t>
+          <t>319677</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5944,12 +5944,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,31%</t>
         </is>
       </c>
     </row>
@@ -5972,12 +5972,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10112</t>
+          <t>9963</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27464</t>
+          <t>26649</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5987,12 +5987,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6007,12 +6007,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7283</t>
+          <t>6713</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>24350</t>
+          <t>23299</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6022,12 +6022,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6042,12 +6042,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>21582</t>
+          <t>21482</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>43847</t>
+          <t>44137</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6057,12 +6057,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -6085,12 +6085,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>183214</t>
+          <t>183524</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>231854</t>
+          <t>233544</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6100,12 +6100,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6120,12 +6120,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>103193</t>
+          <t>101413</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>144425</t>
+          <t>145491</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6135,12 +6135,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6155,12 +6155,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>298490</t>
+          <t>295563</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>362635</t>
+          <t>364620</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6170,12 +6170,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,89%</t>
         </is>
       </c>
     </row>
@@ -6315,12 +6315,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>860654</t>
+          <t>861442</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>954164</t>
+          <t>954684</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6330,12 +6330,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>41,49%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>45,98%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6350,12 +6350,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1046588</t>
+          <t>1047831</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1136377</t>
+          <t>1137378</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6365,12 +6365,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>52,69%</t>
+          <t>52,76%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>57,21%</t>
+          <t>57,26%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1929035</t>
+          <t>1927860</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2058839</t>
+          <t>2065770</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6400,12 +6400,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>47,48%</t>
+          <t>47,45%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>50,85%</t>
         </is>
       </c>
     </row>
@@ -6428,12 +6428,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>321110</t>
+          <t>318340</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>391895</t>
+          <t>389419</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6443,12 +6443,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6463,12 +6463,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>204093</t>
+          <t>202647</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>265709</t>
+          <t>262482</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6478,12 +6478,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6498,12 +6498,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>545256</t>
+          <t>539789</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>636844</t>
+          <t>633942</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6513,12 +6513,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,6%</t>
         </is>
       </c>
     </row>
@@ -6541,12 +6541,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39503</t>
+          <t>39550</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>68402</t>
+          <t>67888</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6561,7 +6561,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30135</t>
+          <t>31028</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>54823</t>
+          <t>55598</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6591,12 +6591,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6611,12 +6611,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>77385</t>
+          <t>76721</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>117543</t>
+          <t>115150</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6626,12 +6626,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -6654,12 +6654,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>721829</t>
+          <t>717262</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>807225</t>
+          <t>806237</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6669,12 +6669,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6689,12 +6689,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>581626</t>
+          <t>580360</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660867</t>
+          <t>662078</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1326443</t>
+          <t>1321267</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1442396</t>
+          <t>1448138</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>35,65%</t>
         </is>
       </c>
     </row>
@@ -6884,12 +6884,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>280454</t>
+          <t>281677</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>329921</t>
+          <t>328430</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6899,12 +6899,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>51,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>60,45%</t>
+          <t>60,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6919,12 +6919,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>301111</t>
+          <t>297551</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>347557</t>
+          <t>344718</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6934,12 +6934,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>54,93%</t>
+          <t>54,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,4%</t>
+          <t>62,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6954,12 +6954,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>594864</t>
+          <t>591543</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>660147</t>
+          <t>658852</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6969,12 +6969,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>54,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,34%</t>
+          <t>60,22%</t>
         </is>
       </c>
     </row>
@@ -6997,12 +6997,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>82704</t>
+          <t>80964</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>120441</t>
+          <t>120124</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7012,12 +7012,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7032,12 +7032,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>84734</t>
+          <t>85840</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>124410</t>
+          <t>125316</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>175589</t>
+          <t>178711</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>229800</t>
+          <t>231436</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,15%</t>
         </is>
       </c>
     </row>
@@ -7110,12 +7110,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11693</t>
+          <t>12576</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30525</t>
+          <t>31279</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7125,12 +7125,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7145,12 +7145,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10427</t>
+          <t>10688</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26521</t>
+          <t>27901</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27820</t>
+          <t>27722</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>52078</t>
+          <t>52002</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -7223,12 +7223,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>100178</t>
+          <t>101329</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>139165</t>
+          <t>142483</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7238,12 +7238,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7258,12 +7258,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>86737</t>
+          <t>87213</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>123064</t>
+          <t>122523</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7293,12 +7293,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>197178</t>
+          <t>196856</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>253940</t>
+          <t>252322</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,06%</t>
         </is>
       </c>
     </row>
@@ -7453,12 +7453,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1442482</t>
+          <t>1441295</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1559077</t>
+          <t>1557297</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7468,12 +7468,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>42,7%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>46,19%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7488,12 +7488,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2156465</t>
+          <t>2167632</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2280118</t>
+          <t>2285208</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>61,15%</t>
+          <t>61,46%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>64,65%</t>
+          <t>64,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3635769</t>
+          <t>3639175</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3807891</t>
+          <t>3812252</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>52,72%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>55,17%</t>
+          <t>55,23%</t>
         </is>
       </c>
     </row>
@@ -7566,12 +7566,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>647539</t>
+          <t>645827</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>744702</t>
+          <t>745597</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7581,12 +7581,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7601,12 +7601,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>347254</t>
+          <t>349829</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>425013</t>
+          <t>428037</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7636,12 +7636,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1019508</t>
+          <t>1016450</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1139393</t>
+          <t>1140007</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,52%</t>
         </is>
       </c>
     </row>
@@ -7679,12 +7679,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>73238</t>
+          <t>73470</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>111701</t>
+          <t>111343</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7714,12 +7714,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>57668</t>
+          <t>58138</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>91633</t>
+          <t>92860</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7749,12 +7749,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>140258</t>
+          <t>140159</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>191828</t>
+          <t>193895</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7769,7 +7769,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -7792,12 +7792,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1036019</t>
+          <t>1030176</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1147251</t>
+          <t>1145222</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7827,12 +7827,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>799088</t>
+          <t>797141</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>899732</t>
+          <t>897566</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7862,12 +7862,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1862140</t>
+          <t>1855003</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2013125</t>
+          <t>2013218</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7877,7 +7877,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">

--- a/data/trans_orig/P23-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P23-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>319057</t>
+          <t>321166</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>379062</t>
+          <t>382785</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1062291</t>
+          <t>1061698</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1114560</t>
+          <t>1115114</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>80,78%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1391396</t>
+          <t>1388244</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1481557</t>
+          <t>1480127</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>59,31%</t>
+          <t>59,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>63,1%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>279275</t>
+          <t>275695</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>339888</t>
+          <t>336907</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>37168</t>
+          <t>38239</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>66134</t>
+          <t>66869</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>326903</t>
+          <t>325476</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>391990</t>
+          <t>394234</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,81%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10353</t>
+          <t>10492</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27357</t>
+          <t>27531</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4257</t>
+          <t>4168</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16682</t>
+          <t>17210</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>18004</t>
+          <t>16997</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>39617</t>
+          <t>38773</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>327110</t>
+          <t>325647</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>386572</t>
+          <t>390300</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>143465</t>
+          <t>144739</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>191107</t>
+          <t>193590</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>484460</t>
+          <t>483048</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>567600</t>
+          <t>564972</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,08%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>600144</t>
+          <t>597878</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>682780</t>
+          <t>676368</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>846842</t>
+          <t>846281</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>924305</t>
+          <t>926069</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>53,34%</t>
+          <t>53,3%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>58,33%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1470001</t>
+          <t>1470448</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1586542</t>
+          <t>1584180</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>44,82%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>48,28%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>209920</t>
+          <t>211461</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>266912</t>
+          <t>268320</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>132240</t>
+          <t>131327</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>179581</t>
+          <t>177629</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>355563</t>
+          <t>352546</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>428692</t>
+          <t>427151</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,02%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35663</t>
+          <t>36179</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>62949</t>
+          <t>64642</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>38441</t>
+          <t>37029</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>65468</t>
+          <t>63241</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>81744</t>
+          <t>81253</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>120177</t>
+          <t>117951</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>725438</t>
+          <t>726068</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>809888</t>
+          <t>803632</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>42,88%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>47,46%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>463378</t>
+          <t>463286</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>536546</t>
+          <t>534779</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1211017</t>
+          <t>1210365</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1321042</t>
+          <t>1321402</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>36,89%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>40,27%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>248436</t>
+          <t>250945</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>296222</t>
+          <t>298852</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>45,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>54,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>266561</t>
+          <t>262908</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>309076</t>
+          <t>307879</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>64,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>528022</t>
+          <t>530570</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>593386</t>
+          <t>593906</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>51,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>57,73%</t>
+          <t>57,78%</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>68195</t>
+          <t>69231</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>102422</t>
+          <t>101511</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>38040</t>
+          <t>38847</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>65233</t>
+          <t>66436</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>114911</t>
+          <t>115089</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>159466</t>
+          <t>158588</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,43%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10830</t>
+          <t>11289</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28374</t>
+          <t>28676</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17285</t>
+          <t>16887</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>37158</t>
+          <t>37015</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32963</t>
+          <t>32453</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>60060</t>
+          <t>59602</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,8%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>153522</t>
+          <t>152296</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>198588</t>
+          <t>196357</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>94150</t>
+          <t>94602</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>130995</t>
+          <t>132990</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>255563</t>
+          <t>256457</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>315554</t>
+          <t>312125</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,37%</t>
         </is>
       </c>
     </row>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1203141</t>
+          <t>1205655</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1316105</t>
+          <t>1315444</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2202130</t>
+          <t>2206620</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2308664</t>
+          <t>2314695</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>65,17%</t>
+          <t>65,3%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>68,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3439197</t>
+          <t>3434129</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3600392</t>
+          <t>3602434</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
+          <t>51,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>54,13%</t>
         </is>
       </c>
     </row>
@@ -2552,12 +2552,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>584210</t>
+          <t>582012</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>674534</t>
+          <t>674906</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2587,12 +2587,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>227951</t>
+          <t>226717</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>286169</t>
+          <t>289190</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>831198</t>
+          <t>837182</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>939920</t>
+          <t>943162</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,17%</t>
         </is>
       </c>
     </row>
@@ -2665,12 +2665,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>70808</t>
+          <t>67232</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>106217</t>
+          <t>103429</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>68275</t>
+          <t>68090</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>102893</t>
+          <t>102122</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>145101</t>
+          <t>143237</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>197464</t>
+          <t>196376</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1246038</t>
+          <t>1244689</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1358779</t>
+          <t>1356023</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>41,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>734624</t>
+          <t>733772</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>826978</t>
+          <t>830312</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2001220</t>
+          <t>2007914</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2163486</t>
+          <t>2158918</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,44%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>222009</t>
+          <t>222892</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>280882</t>
+          <t>276484</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1037062</t>
+          <t>1037276</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1094126</t>
+          <t>1097501</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1270853</t>
+          <t>1266096</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1364848</t>
+          <t>1363627</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>54,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>58,97%</t>
         </is>
       </c>
     </row>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>358530</t>
+          <t>360032</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>422426</t>
+          <t>422994</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3367,12 +3367,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>43,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3387,12 +3387,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>56718</t>
+          <t>57302</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>91721</t>
+          <t>90532</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3422,12 +3422,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>422254</t>
+          <t>420574</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>500473</t>
+          <t>501811</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,7%</t>
         </is>
       </c>
     </row>
@@ -3465,12 +3465,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10433</t>
+          <t>10877</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29103</t>
+          <t>31314</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3480,12 +3480,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3500,12 +3500,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4116</t>
+          <t>4072</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15270</t>
+          <t>16330</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3515,47 +3515,47 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
+          <t>1,22%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>26306</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>17462</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>39249</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
           <t>1,14%</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>26306</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>17028</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>39430</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -3578,12 +3578,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>290049</t>
+          <t>286531</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>346980</t>
+          <t>346072</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3613,12 +3613,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>165253</t>
+          <t>166696</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>215774</t>
+          <t>219039</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3628,12 +3628,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3648,12 +3648,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>470650</t>
+          <t>469951</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>549617</t>
+          <t>549031</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3663,12 +3663,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,74%</t>
         </is>
       </c>
     </row>
@@ -3808,12 +3808,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>711715</t>
+          <t>713035</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>797689</t>
+          <t>799409</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3843,12 +3843,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>831181</t>
+          <t>833309</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>919061</t>
+          <t>919255</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>47,46%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>52,34%</t>
+          <t>52,35%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3878,12 +3878,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1561788</t>
+          <t>1571621</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1691670</t>
+          <t>1691016</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>45,47%</t>
         </is>
       </c>
     </row>
@@ -3921,12 +3921,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>318078</t>
+          <t>315961</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>387303</t>
+          <t>383803</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3936,12 +3936,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3956,12 +3956,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>212901</t>
+          <t>213947</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>274002</t>
+          <t>273910</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3971,12 +3971,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3991,12 +3991,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>554733</t>
+          <t>551516</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>645095</t>
+          <t>642675</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4006,12 +4006,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,28%</t>
         </is>
       </c>
     </row>
@@ -4034,12 +4034,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>44767</t>
+          <t>43670</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>74153</t>
+          <t>74068</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4049,12 +4049,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>35653</t>
+          <t>35095</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>64597</t>
+          <t>64221</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>86272</t>
+          <t>87375</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>127159</t>
+          <t>129310</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4119,12 +4119,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -4147,12 +4147,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>753386</t>
+          <t>755957</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>843391</t>
+          <t>842947</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4162,12 +4162,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>38,51%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>545517</t>
+          <t>548651</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>629208</t>
+          <t>627175</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4197,12 +4197,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1331262</t>
+          <t>1323675</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1443917</t>
+          <t>1451037</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4232,12 +4232,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>35,59%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>39,02%</t>
         </is>
       </c>
     </row>
@@ -4377,12 +4377,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>199605</t>
+          <t>201310</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>245418</t>
+          <t>247310</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4392,12 +4392,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>41,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>217064</t>
+          <t>218293</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>263390</t>
+          <t>261878</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4427,12 +4427,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>47,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,43%</t>
+          <t>57,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>432392</t>
+          <t>430725</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>499273</t>
+          <t>497462</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4462,12 +4462,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>45,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>52,93%</t>
         </is>
       </c>
     </row>
@@ -4490,12 +4490,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>79506</t>
+          <t>79147</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>117488</t>
+          <t>116435</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4505,12 +4505,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>62577</t>
+          <t>62930</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>96674</t>
+          <t>100278</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4540,12 +4540,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>153467</t>
+          <t>150107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>204606</t>
+          <t>200767</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4575,12 +4575,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,36%</t>
         </is>
       </c>
     </row>
@@ -4603,12 +4603,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11701</t>
+          <t>11875</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29904</t>
+          <t>31290</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4618,12 +4618,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4638,12 +4638,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10002</t>
+          <t>10503</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26689</t>
+          <t>28318</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4653,12 +4653,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4673,12 +4673,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>26205</t>
+          <t>25286</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>52154</t>
+          <t>50715</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4688,12 +4688,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -4716,12 +4716,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>123805</t>
+          <t>122853</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>166070</t>
+          <t>165346</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4731,12 +4731,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4751,12 +4751,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>103377</t>
+          <t>103244</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>144601</t>
+          <t>144017</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4766,12 +4766,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4786,12 +4786,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>232267</t>
+          <t>235154</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>292236</t>
+          <t>294105</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4801,12 +4801,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>31,29%</t>
         </is>
       </c>
     </row>
@@ -4946,12 +4946,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1166193</t>
+          <t>1172043</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1283401</t>
+          <t>1282389</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4961,12 +4961,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4981,12 +4981,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2121879</t>
+          <t>2116230</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2242001</t>
+          <t>2239430</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4996,12 +4996,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>59,73%</t>
+          <t>59,57%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>63,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5016,12 +5016,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3326348</t>
+          <t>3332828</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3494725</t>
+          <t>3493949</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>50,12%</t>
         </is>
       </c>
     </row>
@@ -5059,12 +5059,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>786706</t>
+          <t>790773</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>893038</t>
+          <t>891512</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5074,12 +5074,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5094,12 +5094,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>356040</t>
+          <t>357083</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>432779</t>
+          <t>435311</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5109,12 +5109,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1162151</t>
+          <t>1165546</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1298074</t>
+          <t>1294899</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5144,12 +5144,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,58%</t>
         </is>
       </c>
     </row>
@@ -5172,12 +5172,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>75557</t>
+          <t>78488</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>116205</t>
+          <t>120712</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5187,12 +5187,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5207,12 +5207,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>57773</t>
+          <t>57548</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>92297</t>
+          <t>94694</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5222,12 +5222,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5242,12 +5242,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>144431</t>
+          <t>145257</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>198152</t>
+          <t>197215</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5257,12 +5257,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -5285,12 +5285,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1202577</t>
+          <t>1197860</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1315793</t>
+          <t>1315854</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5300,7 +5300,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -5320,12 +5320,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>851364</t>
+          <t>849482</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>960543</t>
+          <t>956823</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5335,12 +5335,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2080552</t>
+          <t>2077173</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2241575</t>
+          <t>2234433</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5370,12 +5370,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>32,05%</t>
         </is>
       </c>
     </row>
@@ -5746,12 +5746,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>262805</t>
+          <t>261637</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>316716</t>
+          <t>314372</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5761,12 +5761,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>41,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>780563</t>
+          <t>780325</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>833736</t>
+          <t>833189</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5816,12 +5816,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1055490</t>
+          <t>1055140</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1136592</t>
+          <t>1137003</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5831,12 +5831,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>60,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,11%</t>
+          <t>65,13%</t>
         </is>
       </c>
     </row>
@@ -5859,12 +5859,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>216545</t>
+          <t>216843</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>265668</t>
+          <t>264760</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5874,12 +5874,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>35961</t>
+          <t>35416</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>64097</t>
+          <t>62230</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5909,12 +5909,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>260530</t>
+          <t>258264</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>319677</t>
+          <t>318115</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5944,12 +5944,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,22%</t>
         </is>
       </c>
     </row>
@@ -5972,12 +5972,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9963</t>
+          <t>10400</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26649</t>
+          <t>27010</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5987,12 +5987,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6007,12 +6007,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6713</t>
+          <t>6935</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>23299</t>
+          <t>22942</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6022,12 +6022,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6042,12 +6042,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>21482</t>
+          <t>21173</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>44137</t>
+          <t>44606</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6057,12 +6057,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -6085,12 +6085,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>183524</t>
+          <t>184974</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>233544</t>
+          <t>233720</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6100,12 +6100,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6120,12 +6120,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>101413</t>
+          <t>104907</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>145491</t>
+          <t>148077</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6135,12 +6135,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6155,12 +6155,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>295563</t>
+          <t>302782</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>364620</t>
+          <t>365139</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6170,12 +6170,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,92%</t>
         </is>
       </c>
     </row>
@@ -6315,12 +6315,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>861442</t>
+          <t>861305</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>954684</t>
+          <t>954786</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6330,7 +6330,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>41,48%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -6350,12 +6350,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1047831</t>
+          <t>1050365</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1137378</t>
+          <t>1138503</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6365,12 +6365,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>52,88%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>57,26%</t>
+          <t>57,32%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1927860</t>
+          <t>1938759</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2065770</t>
+          <t>2061441</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6400,12 +6400,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>47,72%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>50,74%</t>
         </is>
       </c>
     </row>
@@ -6428,12 +6428,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>318340</t>
+          <t>318879</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>389419</t>
+          <t>389981</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6443,12 +6443,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6463,12 +6463,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>202647</t>
+          <t>205177</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>262482</t>
+          <t>260051</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6478,12 +6478,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6498,12 +6498,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>539789</t>
+          <t>542363</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>633942</t>
+          <t>633379</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6513,12 +6513,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,59%</t>
         </is>
       </c>
     </row>
@@ -6541,12 +6541,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39550</t>
+          <t>39406</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>67888</t>
+          <t>70759</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6561,7 +6561,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31028</t>
+          <t>30681</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>55598</t>
+          <t>57557</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6591,12 +6591,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6611,12 +6611,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>76721</t>
+          <t>76231</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>115150</t>
+          <t>117047</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6626,12 +6626,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -6654,12 +6654,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>717262</t>
+          <t>717729</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>806237</t>
+          <t>803840</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6669,12 +6669,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6689,12 +6689,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>580360</t>
+          <t>576945</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>662078</t>
+          <t>661061</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1321267</t>
+          <t>1321425</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1448138</t>
+          <t>1440733</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>35,46%</t>
         </is>
       </c>
     </row>
@@ -6884,12 +6884,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>281677</t>
+          <t>280408</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>328430</t>
+          <t>330468</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6899,12 +6899,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>60,17%</t>
+          <t>60,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6919,12 +6919,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>297551</t>
+          <t>295298</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>344718</t>
+          <t>342495</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6934,12 +6934,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>53,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>62,88%</t>
+          <t>62,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6954,12 +6954,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>591543</t>
+          <t>595194</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>658852</t>
+          <t>661865</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6969,12 +6969,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,07%</t>
+          <t>54,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,22%</t>
+          <t>60,5%</t>
         </is>
       </c>
     </row>
@@ -6997,12 +6997,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>80964</t>
+          <t>82869</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>120124</t>
+          <t>121611</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7012,12 +7012,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7032,12 +7032,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>85840</t>
+          <t>87947</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>125316</t>
+          <t>126586</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>178711</t>
+          <t>176912</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>231436</t>
+          <t>229442</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>20,97%</t>
         </is>
       </c>
     </row>
@@ -7110,12 +7110,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12576</t>
+          <t>11662</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31279</t>
+          <t>31178</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7125,12 +7125,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7145,12 +7145,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10688</t>
+          <t>11268</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27901</t>
+          <t>27451</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27722</t>
+          <t>27772</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>52002</t>
+          <t>51977</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7195,7 +7195,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -7223,12 +7223,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>101329</t>
+          <t>101297</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>142483</t>
+          <t>143174</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7243,7 +7243,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7258,12 +7258,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>87213</t>
+          <t>87401</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>122523</t>
+          <t>123894</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7293,12 +7293,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>196856</t>
+          <t>197730</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>252322</t>
+          <t>250071</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>22,86%</t>
         </is>
       </c>
     </row>
@@ -7453,12 +7453,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1441295</t>
+          <t>1450234</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1557297</t>
+          <t>1560397</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7468,12 +7468,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>46,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7488,12 +7488,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2167632</t>
+          <t>2158699</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2285208</t>
+          <t>2285098</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>61,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>64,8%</t>
+          <t>64,79%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3639175</t>
+          <t>3646392</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3812252</t>
+          <t>3810888</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>52,72%</t>
+          <t>52,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>55,23%</t>
+          <t>55,21%</t>
         </is>
       </c>
     </row>
@@ -7566,12 +7566,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>645827</t>
+          <t>644164</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>745597</t>
+          <t>740112</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7581,12 +7581,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7601,12 +7601,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>349829</t>
+          <t>348857</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>428037</t>
+          <t>426510</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7636,12 +7636,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1016450</t>
+          <t>1021184</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1140007</t>
+          <t>1141955</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,54%</t>
         </is>
       </c>
     </row>
@@ -7679,12 +7679,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>73470</t>
+          <t>72747</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>111343</t>
+          <t>113381</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7714,12 +7714,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>58138</t>
+          <t>56808</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>92860</t>
+          <t>90274</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7749,12 +7749,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>140159</t>
+          <t>139200</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>193895</t>
+          <t>190605</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -7792,12 +7792,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1030176</t>
+          <t>1031354</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1145222</t>
+          <t>1141236</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7827,12 +7827,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>797141</t>
+          <t>793206</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>897566</t>
+          <t>900675</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7862,12 +7862,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1855003</t>
+          <t>1868767</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2013218</t>
+          <t>2011478</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>29,14%</t>
         </is>
       </c>
     </row>
